--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>47.52</v>
+        <v>48.56</v>
       </c>
       <c r="C2">
-        <v>41.08</v>
+        <v>41.48</v>
       </c>
       <c r="D2">
-        <v>7.268623024830701</v>
+        <v>7.863171923589513</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="H2">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="I2">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="J2">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="K2">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="L2">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="M2">
-        <v>2.92</v>
+        <v>2.920000000000006</v>
       </c>
       <c r="N2">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="O2">
-        <v>7.268623024830707</v>
+        <v>7.863171923589517</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>48.56</v>
+        <v>48.92</v>
       </c>
       <c r="C2">
-        <v>41.48</v>
+        <v>41.06</v>
       </c>
       <c r="D2">
-        <v>7.863171923589513</v>
+        <v>8.735274505445654</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>52.35678365171034</v>
+        <v>52.78010224494333</v>
       </c>
       <c r="H2">
-        <v>44.72321634828965</v>
+        <v>44.29989775505667</v>
       </c>
       <c r="I2">
-        <v>52.35678365171034</v>
+        <v>52.78010224494333</v>
       </c>
       <c r="J2">
-        <v>44.72321634828965</v>
+        <v>44.29989775505667</v>
       </c>
       <c r="K2">
-        <v>52.35678365171034</v>
+        <v>52.78010224494333</v>
       </c>
       <c r="L2">
-        <v>44.72321634828965</v>
+        <v>44.29989775505667</v>
       </c>
       <c r="M2">
-        <v>2.920000000000006</v>
+        <v>2.92</v>
       </c>
       <c r="N2">
-        <v>7.633567303420702</v>
+        <v>8.480204489886656</v>
       </c>
       <c r="O2">
-        <v>7.863171923589517</v>
+        <v>8.73527450544567</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>48.92</v>
+        <v>49</v>
       </c>
       <c r="C2">
-        <v>41.06</v>
+        <v>41.14</v>
       </c>
       <c r="D2">
-        <v>8.735274505445654</v>
+        <v>8.719769247836698</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>52.78010224494333</v>
+        <v>52.77257599289993</v>
       </c>
       <c r="H2">
-        <v>44.29989775505667</v>
+        <v>44.30742400710007</v>
       </c>
       <c r="I2">
-        <v>52.78010224494333</v>
+        <v>52.77257599289993</v>
       </c>
       <c r="J2">
-        <v>44.29989775505667</v>
+        <v>44.30742400710007</v>
       </c>
       <c r="K2">
-        <v>52.78010224494333</v>
+        <v>52.77257599289993</v>
       </c>
       <c r="L2">
-        <v>44.29989775505667</v>
+        <v>44.30742400710007</v>
       </c>
       <c r="M2">
         <v>2.92</v>
       </c>
       <c r="N2">
-        <v>8.480204489886656</v>
+        <v>8.465151985799857</v>
       </c>
       <c r="O2">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>49</v>
+        <v>49.14</v>
       </c>
       <c r="C2">
-        <v>41.14</v>
+        <v>41.48</v>
       </c>
       <c r="D2">
-        <v>8.719769247836698</v>
+        <v>8.45288015890532</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>52.77257599289993</v>
+        <v>52.64302802913263</v>
       </c>
       <c r="H2">
-        <v>44.30742400710007</v>
+        <v>44.43697197086736</v>
       </c>
       <c r="I2">
-        <v>52.77257599289993</v>
+        <v>52.64302802913263</v>
       </c>
       <c r="J2">
-        <v>44.30742400710007</v>
+        <v>44.43697197086736</v>
       </c>
       <c r="K2">
-        <v>52.77257599289993</v>
+        <v>52.64302802913263</v>
       </c>
       <c r="L2">
-        <v>44.30742400710007</v>
+        <v>44.43697197086736</v>
       </c>
       <c r="M2">
-        <v>2.92</v>
+        <v>2.920000000000006</v>
       </c>
       <c r="N2">
-        <v>8.465151985799857</v>
+        <v>8.20605605826527</v>
       </c>
       <c r="O2">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>49.14</v>
+        <v>49.64</v>
       </c>
       <c r="C2">
-        <v>41.48</v>
+        <v>41.36</v>
       </c>
       <c r="D2">
-        <v>8.45288015890532</v>
+        <v>9.098901098901097</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>52.64302802913263</v>
+        <v>52.9566065934066</v>
       </c>
       <c r="H2">
-        <v>44.43697197086736</v>
+        <v>44.1233934065934</v>
       </c>
       <c r="I2">
-        <v>52.64302802913263</v>
+        <v>52.9566065934066</v>
       </c>
       <c r="J2">
-        <v>44.43697197086736</v>
+        <v>44.1233934065934</v>
       </c>
       <c r="K2">
-        <v>52.64302802913263</v>
+        <v>52.9566065934066</v>
       </c>
       <c r="L2">
-        <v>44.43697197086736</v>
+        <v>44.1233934065934</v>
       </c>
       <c r="M2">
-        <v>2.920000000000006</v>
+        <v>2.92</v>
       </c>
       <c r="N2">
-        <v>8.20605605826527</v>
+        <v>8.833213186813193</v>
       </c>
       <c r="O2">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>49.64</v>
+        <v>49.9</v>
       </c>
       <c r="C2">
-        <v>41.36</v>
+        <v>41.84</v>
       </c>
       <c r="D2">
-        <v>9.098901098901097</v>
+        <v>8.785698713756268</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="H2">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="I2">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="J2">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="K2">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="L2">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="M2">
-        <v>2.92</v>
+        <v>2.919999999999995</v>
       </c>
       <c r="N2">
-        <v>8.833213186813193</v>
+        <v>8.529156311314573</v>
       </c>
       <c r="O2">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
     </row>
   </sheetData>
